--- a/jogos_2024-09-09.xlsx
+++ b/jogos_2024-09-09.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>2.58</v>
       </c>
       <c r="N5" t="n">
-        <v>2.2</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="T5" t="n">
-        <v>2.75</v>
+        <v>3.72</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="X5" t="n">
-        <v>3.48</v>
+        <v>2.15</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.75</v>
+        <v>2.72</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.05</v>
+        <v>1.38</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.98</v>
+        <v>5.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.62</v>
+        <v>2.32</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.2</v>
+        <v>1.54</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['34', '41', '48']</t>
+          <t>['35', '42']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '39']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.69</v>
+        <v>1.35</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45544.54166666666</v>
@@ -1159,109 +1159,109 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Umm al-Fahm</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA6" t="n">
         <v>3.5</v>
       </c>
-      <c r="T6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.32</v>
-      </c>
       <c r="AB6" t="n">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['43', '65', '90+7']</t>
+          <t>['35', '45']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>['10']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.07</v>
+        <v>1.48</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.3</v>
+        <v>1.38</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45544.54166666666</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="M7" t="n">
-        <v>2.58</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>3.15</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
-        <v>3.56</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['34', '41', '48']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.73</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>['35', '42']</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>['8', '39']</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>2.3</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45544.54166666666</v>
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Umm al-Fahm</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S8" t="n">
         <v>3.5</v>
       </c>
-      <c r="O8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="V8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="X8" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD8" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['35', '45']</t>
+          <t>['43', '65', '90+7']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['10']</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.48</v>
+        <v>1.07</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.38</v>
+        <v>3.3</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45544.54166666666</v>
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Sloboda Užice</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Inđija</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>2</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="M9" t="n">
         <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="O9" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W9" t="n">
         <v>1.33</v>
       </c>
-      <c r="S9" t="n">
+      <c r="X9" t="n">
         <v>3</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W9" t="n">
+      <c r="Y9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.2</v>
       </c>
-      <c r="X9" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AC9" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['77', '90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43', '62']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45544.5625</v>
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sloboda Užice</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Inđija</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
         <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="M10" t="n">
         <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="O10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.75</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="U10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X10" t="n">
         <v>4</v>
       </c>
-      <c r="R10" t="n">
+      <c r="Y10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['77', '90+2']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
         <v>1.44</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['43', '62']</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45544.5625</v>
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2223,10 +2223,10 @@
         <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="P14" t="n">
         <v>2.1</v>
@@ -2241,53 +2241,53 @@
         <v>2.63</v>
       </c>
       <c r="T14" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="X14" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AA14" t="n">
         <v>3.28</v>
       </c>
-      <c r="Y14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.81</v>
-      </c>
       <c r="AB14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['18']</t>
+          <t>['49', '53', '56']</t>
         </is>
       </c>
       <c r="AG14" t="n">
         <v>1.35</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AI14" t="n">
         <v>1.73</v>
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
         <v>1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>3</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2352,10 +2352,10 @@
         <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
         <v>2.1</v>
@@ -2370,53 +2370,53 @@
         <v>2.63</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="X15" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="Y15" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.28</v>
+        <v>3.81</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['49', '53', '56']</t>
+          <t>['18']</t>
         </is>
       </c>
       <c r="AG15" t="n">
         <v>1.35</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AI15" t="n">
         <v>1.73</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>4.75</v>
+        <v>2.4</v>
       </c>
       <c r="O16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC16" t="n">
         <v>2.38</v>
       </c>
-      <c r="P16" t="n">
+      <c r="AD16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X16" t="n">
+      <c r="AJ16" t="n">
         <v>2.38</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['59', '85']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['41', '48']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>3.5</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45544.83333333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>1.68</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.4</v>
+        <v>4.75</v>
       </c>
       <c r="O17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['59', '85']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['41', '48']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>3.5</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>4</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['83']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>2.38</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45544.83333333334</v>
